--- a/assets/ASIENTOS_CONTABLES_CABECERA2.xlsx
+++ b/assets/ASIENTOS_CONTABLES_CABECERA2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\proyecto4\OneDrive - LLAMA GAS S.A\Documentos\GitHub\Jobs_JE\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://llamgas-my.sharepoint.com/personal/analista_proyectos_grupollamagas_pe/Documents/Documentos/GitHub/Jobs_JE/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D0A534-DD33-4DFF-A792-46480B940D11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{60D0A534-DD33-4DFF-A792-46480B940D11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A890074-B131-4EE6-BC01-B3F00057E135}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-975" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CabeceraSaldosBancosFinal" sheetId="4" r:id="rId1"/>
@@ -127,13 +127,13 @@
     <t>Codigo proyecto</t>
   </si>
   <si>
-    <t>Saldos de planillas Mes de Julio</t>
-  </si>
-  <si>
-    <t>20250731</t>
-  </si>
-  <si>
     <t>PLAM</t>
+  </si>
+  <si>
+    <t>Saldos de planillas Mes de MARZO</t>
+  </si>
+  <si>
+    <t>20260319</t>
   </si>
 </sst>
 </file>
@@ -604,19 +604,19 @@
         <v>1</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
